--- a/assets/db_review_product.xlsx
+++ b/assets/db_review_product.xlsx
@@ -3,8 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="produk" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="review" sheetId="2" r:id="rId6"/>
+    <sheet state="visible" name="kategori" sheetId="1" r:id="rId5"/>
+    <sheet state="visible" name="produk" sheetId="2" r:id="rId6"/>
+    <sheet state="visible" name="review" sheetId="3" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -12,17 +13,146 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="259">
   <si>
     <t>id</t>
   </si>
   <si>
+    <t>nama_kategori</t>
+  </si>
+  <si>
+    <t>slug</t>
+  </si>
+  <si>
+    <t>icon</t>
+  </si>
+  <si>
+    <t>warna</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>Smartphone</t>
+  </si>
+  <si>
+    <t>smartphone</t>
+  </si>
+  <si>
+    <t>fa-mobile-screen</t>
+  </si>
+  <si>
+    <t>primary</t>
+  </si>
+  <si>
+    <t>Aktif</t>
+  </si>
+  <si>
+    <t>Laptop</t>
+  </si>
+  <si>
+    <t>laptop</t>
+  </si>
+  <si>
+    <t>fa-laptop</t>
+  </si>
+  <si>
+    <t>success</t>
+  </si>
+  <si>
+    <t>Kamera</t>
+  </si>
+  <si>
+    <t>kamera</t>
+  </si>
+  <si>
+    <t>fa-camera</t>
+  </si>
+  <si>
+    <t>danger</t>
+  </si>
+  <si>
+    <t>Aksesoris</t>
+  </si>
+  <si>
+    <t>aksesoris</t>
+  </si>
+  <si>
+    <t>fa-headphones</t>
+  </si>
+  <si>
+    <t>warning</t>
+  </si>
+  <si>
+    <t>Smartwatch</t>
+  </si>
+  <si>
+    <t>smartwatch</t>
+  </si>
+  <si>
+    <t>fa-clock</t>
+  </si>
+  <si>
+    <t>info</t>
+  </si>
+  <si>
+    <t>Tablet</t>
+  </si>
+  <si>
+    <t>tablet</t>
+  </si>
+  <si>
+    <t>fa-tablet-screen-button</t>
+  </si>
+  <si>
+    <t>secondary</t>
+  </si>
+  <si>
+    <t>Gaming</t>
+  </si>
+  <si>
+    <t>gaming</t>
+  </si>
+  <si>
+    <t>fa-gamepad</t>
+  </si>
+  <si>
+    <t>dark</t>
+  </si>
+  <si>
+    <t>Smart TV</t>
+  </si>
+  <si>
+    <t>smart-tv</t>
+  </si>
+  <si>
+    <t>fa-tv</t>
+  </si>
+  <si>
+    <t>Power &amp; Charger</t>
+  </si>
+  <si>
+    <t>power-charger</t>
+  </si>
+  <si>
+    <t>fa-bolt</t>
+  </si>
+  <si>
+    <t>Printer</t>
+  </si>
+  <si>
+    <t>printer</t>
+  </si>
+  <si>
+    <t>fa-print</t>
+  </si>
+  <si>
+    <t>kategori_id</t>
+  </si>
+  <si>
     <t>nama_produk</t>
   </si>
   <si>
-    <t>kategori</t>
-  </si>
-  <si>
     <t>brand</t>
   </si>
   <si>
@@ -35,25 +165,559 @@
     <t>deskripsi</t>
   </si>
   <si>
-    <t>status</t>
-  </si>
-  <si>
     <t>iPhone 16 Pro</t>
   </si>
   <si>
-    <t>Smartphone</t>
-  </si>
-  <si>
     <t>Apple</t>
   </si>
   <si>
+    <t>https://placehold.co/600x600?text=iPhone+16+Pro</t>
+  </si>
+  <si>
+    <t>Smartphone flagship Apple dengan kamera premium</t>
+  </si>
+  <si>
+    <t>Samsung Galaxy S25 Ultra</t>
+  </si>
+  <si>
+    <t>Samsung</t>
+  </si>
+  <si>
+    <t>https://placehold.co/600x600?text=Galaxy+S25+Ultra</t>
+  </si>
+  <si>
+    <t>Smartphone Android premium untuk produktivitas</t>
+  </si>
+  <si>
+    <t>Xiaomi 15 Pro</t>
+  </si>
+  <si>
+    <t>Xiaomi</t>
+  </si>
+  <si>
+    <t>https://placehold.co/600x600?text=Xiaomi+15+Pro</t>
+  </si>
+  <si>
+    <t>Smartphone performa tinggi dengan fast charging</t>
+  </si>
+  <si>
+    <t>Oppo Find X8 Pro</t>
+  </si>
+  <si>
+    <t>Oppo</t>
+  </si>
+  <si>
+    <t>https://placehold.co/600x600?text=Oppo+Find+X8+Pro</t>
+  </si>
+  <si>
+    <t>Smartphone kamera flagship desain elegan</t>
+  </si>
+  <si>
+    <t>Vivo X200 Pro</t>
+  </si>
+  <si>
+    <t>Vivo</t>
+  </si>
+  <si>
+    <t>https://placehold.co/600x600?text=Vivo+X200+Pro</t>
+  </si>
+  <si>
+    <t>Smartphone fotografi profesional</t>
+  </si>
+  <si>
+    <t>MacBook Air M3</t>
+  </si>
+  <si>
+    <t>https://placehold.co/600x600?text=MacBook+Air+M3</t>
+  </si>
+  <si>
+    <t>Laptop ringan untuk kerja dan kuliah</t>
+  </si>
+  <si>
+    <t>ASUS Zenbook 14</t>
+  </si>
+  <si>
+    <t>ASUS</t>
+  </si>
+  <si>
+    <t>https://placehold.co/600x600?text=ASUS+Zenbook+14</t>
+  </si>
+  <si>
+    <t>Laptop ultrabook tipis dan bertenaga</t>
+  </si>
+  <si>
+    <t>Lenovo ThinkPad X1</t>
+  </si>
+  <si>
+    <t>Lenovo</t>
+  </si>
+  <si>
+    <t>https://placehold.co/600x600?text=ThinkPad+X1</t>
+  </si>
+  <si>
+    <t>Laptop bisnis premium dan tahan lama</t>
+  </si>
+  <si>
+    <t>HP Spectre x360</t>
+  </si>
+  <si>
+    <t>HP</t>
+  </si>
+  <si>
+    <t>https://placehold.co/600x600?text=HP+Spectre+x360</t>
+  </si>
+  <si>
+    <t>Laptop convertible layar sentuh premium</t>
+  </si>
+  <si>
+    <t>Acer Swift Go</t>
+  </si>
+  <si>
+    <t>Acer</t>
+  </si>
+  <si>
+    <t>https://placehold.co/600x600?text=Acer+Swift+Go</t>
+  </si>
+  <si>
+    <t>Laptop ringan untuk produktivitas harian</t>
+  </si>
+  <si>
+    <t>Sony Alpha A6400</t>
+  </si>
+  <si>
+    <t>Sony</t>
+  </si>
+  <si>
+    <t>https://placehold.co/600x600?text=Sony+A6400</t>
+  </si>
+  <si>
+    <t>Kamera mirrorless untuk foto dan video</t>
+  </si>
+  <si>
+    <t>Canon EOS R50</t>
+  </si>
+  <si>
+    <t>Canon</t>
+  </si>
+  <si>
+    <t>https://placehold.co/600x600?text=Canon+EOS+R50</t>
+  </si>
+  <si>
+    <t>Kamera mirrorless cocok untuk kreator</t>
+  </si>
+  <si>
+    <t>Nikon Z30</t>
+  </si>
+  <si>
+    <t>Nikon</t>
+  </si>
+  <si>
+    <t>https://placehold.co/600x600?text=Nikon+Z30</t>
+  </si>
+  <si>
+    <t>Kamera vlog ringan dan praktis</t>
+  </si>
+  <si>
+    <t>Fujifilm X-S20</t>
+  </si>
+  <si>
+    <t>Fujifilm</t>
+  </si>
+  <si>
+    <t>https://placehold.co/600x600?text=Fujifilm+X-S20</t>
+  </si>
+  <si>
+    <t>Kamera hybrid dengan warna khas Fujifilm</t>
+  </si>
+  <si>
+    <t>Panasonic Lumix G100</t>
+  </si>
+  <si>
+    <t>Panasonic</t>
+  </si>
+  <si>
+    <t>https://placehold.co/600x600?text=Lumix+G100</t>
+  </si>
+  <si>
+    <t>Kamera compact untuk video harian</t>
+  </si>
+  <si>
+    <t>AirPods Pro 2</t>
+  </si>
+  <si>
+    <t>https://placehold.co/600x600?text=AirPods+Pro+2</t>
+  </si>
+  <si>
+    <t>Earbuds wireless dengan noise cancelling</t>
+  </si>
+  <si>
+    <t>Samsung Galaxy Buds 3</t>
+  </si>
+  <si>
+    <t>https://placehold.co/600x600?text=Galaxy+Buds+3</t>
+  </si>
+  <si>
+    <t>Earbuds nyaman untuk musik dan telepon</t>
+  </si>
+  <si>
+    <t>Sony WH-1000XM5</t>
+  </si>
+  <si>
+    <t>https://placehold.co/600x600?text=Sony+WH-1000XM5</t>
+  </si>
+  <si>
+    <t>Headphone noise cancelling premium</t>
+  </si>
+  <si>
+    <t>JBL Tune 770NC</t>
+  </si>
+  <si>
+    <t>JBL</t>
+  </si>
+  <si>
+    <t>https://placehold.co/600x600?text=JBL+Tune+770NC</t>
+  </si>
+  <si>
+    <t>Headphone wireless bass kuat</t>
+  </si>
+  <si>
+    <t>Logitech MX Master 3S</t>
+  </si>
+  <si>
+    <t>Logitech</t>
+  </si>
+  <si>
+    <t>https://placehold.co/600x600?text=MX+Master+3S</t>
+  </si>
+  <si>
+    <t>Mouse produktivitas ergonomis</t>
+  </si>
+  <si>
+    <t>Apple Watch Series 10</t>
+  </si>
+  <si>
+    <t>https://placehold.co/600x600?text=Apple+Watch+S10</t>
+  </si>
+  <si>
+    <t>Smartwatch kesehatan dan olahraga</t>
+  </si>
+  <si>
+    <t>Samsung Galaxy Watch 7</t>
+  </si>
+  <si>
+    <t>https://placehold.co/600x600?text=Galaxy+Watch+7</t>
+  </si>
+  <si>
+    <t>Smartwatch Android fitur lengkap</t>
+  </si>
+  <si>
+    <t>Garmin Forerunner 265</t>
+  </si>
+  <si>
+    <t>Garmin</t>
+  </si>
+  <si>
+    <t>https://placehold.co/600x600?text=Garmin+265</t>
+  </si>
+  <si>
+    <t>Jam olahraga untuk pelari serius</t>
+  </si>
+  <si>
+    <t>Huawei Watch GT 5</t>
+  </si>
+  <si>
+    <t>Huawei</t>
+  </si>
+  <si>
+    <t>https://placehold.co/600x600?text=Huawei+Watch+GT5</t>
+  </si>
+  <si>
+    <t>Smartwatch baterai tahan lama</t>
+  </si>
+  <si>
+    <t>Amazfit GTR 4</t>
+  </si>
+  <si>
+    <t>Amazfit</t>
+  </si>
+  <si>
+    <t>https://placehold.co/600x600?text=Amazfit+GTR+4</t>
+  </si>
+  <si>
+    <t>Smartwatch stylish harga terjangkau</t>
+  </si>
+  <si>
+    <t>iPad Air M2</t>
+  </si>
+  <si>
+    <t>https://placehold.co/600x600?text=iPad+Air+M2</t>
+  </si>
+  <si>
+    <t>Tablet ringan untuk belajar dan desain</t>
+  </si>
+  <si>
+    <t>Samsung Galaxy Tab S10</t>
+  </si>
+  <si>
+    <t>https://placehold.co/600x600?text=Galaxy+Tab+S10</t>
+  </si>
+  <si>
+    <t>Tablet Android premium layar luas</t>
+  </si>
+  <si>
+    <t>Xiaomi Pad 6S Pro</t>
+  </si>
+  <si>
+    <t>https://placehold.co/600x600?text=Xiaomi+Pad+6S+Pro</t>
+  </si>
+  <si>
+    <t>Tablet produktivitas harga kompetitif</t>
+  </si>
+  <si>
+    <t>Lenovo Tab P12</t>
+  </si>
+  <si>
+    <t>https://placehold.co/600x600?text=Lenovo+Tab+P12</t>
+  </si>
+  <si>
+    <t>Tablet belajar dan hiburan keluarga</t>
+  </si>
+  <si>
+    <t>Huawei MatePad 11.5</t>
+  </si>
+  <si>
+    <t>https://placehold.co/600x600?text=Huawei+MatePad</t>
+  </si>
+  <si>
+    <t>Tablet tipis dengan layar nyaman</t>
+  </si>
+  <si>
+    <t>PlayStation 5 Slim</t>
+  </si>
+  <si>
+    <t>https://placehold.co/600x600?text=PS5+Slim</t>
+  </si>
+  <si>
+    <t>Konsol gaming generasi terbaru</t>
+  </si>
+  <si>
+    <t>Xbox Series X</t>
+  </si>
+  <si>
+    <t>Microsoft</t>
+  </si>
+  <si>
+    <t>https://placehold.co/600x600?text=Xbox+Series+X</t>
+  </si>
+  <si>
+    <t>Konsol gaming performa tinggi</t>
+  </si>
+  <si>
+    <t>Nintendo Switch OLED</t>
+  </si>
+  <si>
+    <t>Nintendo</t>
+  </si>
+  <si>
+    <t>https://placehold.co/600x600?text=Switch+OLED</t>
+  </si>
+  <si>
+    <t>Konsol portable layar OLED</t>
+  </si>
+  <si>
+    <t>Steam Deck OLED</t>
+  </si>
+  <si>
+    <t>Valve</t>
+  </si>
+  <si>
+    <t>https://placehold.co/600x600?text=Steam+Deck+OLED</t>
+  </si>
+  <si>
+    <t>Handheld gaming PC portable</t>
+  </si>
+  <si>
+    <t>ASUS ROG Ally</t>
+  </si>
+  <si>
+    <t>https://placehold.co/600x600?text=ROG+Ally</t>
+  </si>
+  <si>
+    <t>Handheld gaming Windows</t>
+  </si>
+  <si>
+    <t>LG OLED C4</t>
+  </si>
+  <si>
+    <t>LG</t>
+  </si>
+  <si>
+    <t>https://placehold.co/600x600?text=LG+OLED+C4</t>
+  </si>
+  <si>
+    <t>Smart TV OLED kualitas sinema</t>
+  </si>
+  <si>
+    <t>Samsung Neo QLED</t>
+  </si>
+  <si>
+    <t>https://placehold.co/600x600?text=Samsung+Neo+QLED</t>
+  </si>
+  <si>
+    <t>Smart TV premium resolusi tajam</t>
+  </si>
+  <si>
+    <t>Sony Bravia XR</t>
+  </si>
+  <si>
+    <t>https://placehold.co/600x600?text=Sony+Bravia+XR</t>
+  </si>
+  <si>
+    <t>Smart TV dengan kualitas gambar natural</t>
+  </si>
+  <si>
+    <t>TCL C755 Mini LED</t>
+  </si>
+  <si>
+    <t>TCL</t>
+  </si>
+  <si>
+    <t>https://placehold.co/600x600?text=TCL+C755</t>
+  </si>
+  <si>
+    <t>Smart TV Mini LED harga menarik</t>
+  </si>
+  <si>
+    <t>Xiaomi TV A Pro</t>
+  </si>
+  <si>
+    <t>https://placehold.co/600x600?text=Xiaomi+TV+A+Pro</t>
+  </si>
+  <si>
+    <t>Smart TV terjangkau fitur lengkap</t>
+  </si>
+  <si>
+    <t>Anker PowerCore 20000</t>
+  </si>
+  <si>
+    <t>Anker</t>
+  </si>
+  <si>
+    <t>https://placehold.co/600x600?text=Anker+PowerCore</t>
+  </si>
+  <si>
+    <t>Power bank kapasitas besar</t>
+  </si>
+  <si>
+    <t>Baseus Blade 100W</t>
+  </si>
+  <si>
+    <t>Baseus</t>
+  </si>
+  <si>
+    <t>https://placehold.co/600x600?text=Baseus+Blade</t>
+  </si>
+  <si>
+    <t>Power bank tipis fast charging</t>
+  </si>
+  <si>
+    <t>Ugreen Nexode 65W</t>
+  </si>
+  <si>
+    <t>Ugreen</t>
+  </si>
+  <si>
+    <t>https://placehold.co/600x600?text=Ugreen+Nexode</t>
+  </si>
+  <si>
+    <t>Charger GaN cepat dan compact</t>
+  </si>
+  <si>
+    <t>Robot RT180</t>
+  </si>
+  <si>
+    <t>Robot</t>
+  </si>
+  <si>
+    <t>https://placehold.co/600x600?text=Robot+RT180</t>
+  </si>
+  <si>
+    <t>Charger murah untuk penggunaan harian</t>
+  </si>
+  <si>
+    <t>Vention USB-C Hub</t>
+  </si>
+  <si>
+    <t>Vention</t>
+  </si>
+  <si>
+    <t>https://placehold.co/600x600?text=Vention+Hub</t>
+  </si>
+  <si>
+    <t>Hub USB-C multifungsi</t>
+  </si>
+  <si>
+    <t>Canon Pixma G3010</t>
+  </si>
+  <si>
+    <t>https://placehold.co/600x600?text=Canon+G3010</t>
+  </si>
+  <si>
+    <t>Printer ink tank hemat tinta</t>
+  </si>
+  <si>
+    <t>Epson L3250</t>
+  </si>
+  <si>
+    <t>Epson</t>
+  </si>
+  <si>
+    <t>https://placehold.co/600x600?text=Epson+L3250</t>
+  </si>
+  <si>
+    <t>Printer multifungsi WiFi</t>
+  </si>
+  <si>
+    <t>HP Smart Tank 580</t>
+  </si>
+  <si>
+    <t>https://placehold.co/600x600?text=HP+Smart+Tank</t>
+  </si>
+  <si>
+    <t>Printer rumahan hemat biaya</t>
+  </si>
+  <si>
+    <t>Brother DCP-T720DW</t>
+  </si>
+  <si>
+    <t>Brother</t>
+  </si>
+  <si>
+    <t>https://placehold.co/600x600?text=Brother+T720DW</t>
+  </si>
+  <si>
+    <t>Printer duplex untuk kantor kecil</t>
+  </si>
+  <si>
+    <t>Fujifilm Instax Mini Link</t>
+  </si>
+  <si>
+    <t>https://placehold.co/600x600?text=Instax+Mini+Link</t>
+  </si>
+  <si>
+    <t>Printer foto portable</t>
+  </si>
+  <si>
+    <t>RRR</t>
+  </si>
+  <si>
     <t>https://assets.swappie.com/cdn-cgi/image/width=600,height=600,dpr=2,fit=contain,format=auto/swappie-iphone-16-pro-max-desert-titanium.png?v=7fc3d325</t>
   </si>
   <si>
-    <t>Smartphone flagship Apple</t>
-  </si>
-  <si>
-    <t>Aktif</t>
+    <t>d</t>
+  </si>
+  <si>
+    <t>dadad</t>
   </si>
   <si>
     <t>produk_id</t>
@@ -113,9 +777,6 @@
     <t>Layarnya jernih</t>
   </si>
   <si>
-    <t>dadad</t>
-  </si>
-  <si>
     <t>firdausfirda71@gmail.com</t>
   </si>
   <si>
@@ -129,15 +790,28 @@
   </si>
   <si>
     <t>dsaasdasda</t>
+  </si>
+  <si>
+    <t>dasdasdadads</t>
+  </si>
+  <si>
+    <t>adsad</t>
+  </si>
+  <si>
+    <t>addas</t>
+  </si>
+  <si>
+    <t>dasd</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="m/d/yyyy h:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -176,7 +850,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -189,13 +863,16 @@
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
@@ -211,6 +888,10 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -438,44 +1119,209 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="2">
         <v>1.0</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="2">
-        <v>1.9999E7</v>
-      </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="E3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink r:id="rId1" ref="F2"/>
-  </hyperlinks>
-  <drawing r:id="rId2"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -485,31 +1331,34 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="2" max="2" width="24.88"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2">
@@ -520,22 +1369,22 @@
         <v>1.0</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>22</v>
+        <v>50</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>51</v>
       </c>
       <c r="E2" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>23</v>
+        <v>1.9999E7</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>52</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H2" s="4">
-        <v>46179.0</v>
+        <v>53</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -543,77 +1392,1599 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E3" s="2">
+        <v>1.8999E7</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="B4" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E4" s="2">
+        <v>1.1999E7</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="B5" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E5" s="2">
+        <v>1.3999E7</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="B6" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E6" s="2">
+        <v>1.4999E7</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="B7" s="2">
         <v>2.0</v>
       </c>
+      <c r="C7" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E7" s="2">
+        <v>1.7999E7</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="B8" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E8" s="2">
+        <v>1.4999E7</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="B9" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E9" s="2">
+        <v>2.2999E7</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="B10" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E10" s="2">
+        <v>1.9999E7</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="B11" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E11" s="2">
+        <v>1.0999E7</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2">
+        <v>11.0</v>
+      </c>
+      <c r="B12" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E12" s="2">
+        <v>1.3499E7</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2">
+        <v>12.0</v>
+      </c>
+      <c r="B13" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E13" s="2">
+        <v>1.1999E7</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2">
+        <v>13.0</v>
+      </c>
+      <c r="B14" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E14" s="2">
+        <v>1.0999E7</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2">
+        <v>14.0</v>
+      </c>
+      <c r="B15" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E15" s="2">
+        <v>2.0999E7</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2">
+        <v>15.0</v>
+      </c>
+      <c r="B16" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E16" s="2">
+        <v>9999000.0</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2">
+        <v>16.0</v>
+      </c>
+      <c r="B17" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E17" s="2">
+        <v>3999000.0</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2">
+        <v>17.0</v>
+      </c>
+      <c r="B18" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E18" s="2">
+        <v>2499000.0</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2">
+        <v>18.0</v>
+      </c>
+      <c r="B19" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E19" s="2">
+        <v>5499000.0</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2">
+        <v>19.0</v>
+      </c>
+      <c r="B20" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E20" s="2">
+        <v>1799000.0</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2">
+        <v>20.0</v>
+      </c>
+      <c r="B21" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E21" s="2">
+        <v>1599000.0</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2">
+        <v>21.0</v>
+      </c>
+      <c r="B22" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E22" s="2">
+        <v>6999000.0</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2">
+        <v>22.0</v>
+      </c>
+      <c r="B23" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E23" s="2">
+        <v>4499000.0</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2">
+        <v>23.0</v>
+      </c>
+      <c r="B24" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E24" s="2">
+        <v>7499000.0</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2">
+        <v>24.0</v>
+      </c>
+      <c r="B25" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E25" s="2">
+        <v>3499000.0</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2">
+        <v>25.0</v>
+      </c>
+      <c r="B26" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E26" s="2">
+        <v>2499000.0</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2">
+        <v>26.0</v>
+      </c>
+      <c r="B27" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E27" s="2">
+        <v>1.0999E7</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2">
+        <v>27.0</v>
+      </c>
+      <c r="B28" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E28" s="2">
+        <v>1.2999E7</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2">
+        <v>28.0</v>
+      </c>
+      <c r="B29" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E29" s="2">
+        <v>6999000.0</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2">
+        <v>29.0</v>
+      </c>
+      <c r="B30" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E30" s="2">
+        <v>4999000.0</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2">
+        <v>30.0</v>
+      </c>
+      <c r="B31" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E31" s="2">
+        <v>5999000.0</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2">
+        <v>31.0</v>
+      </c>
+      <c r="B32" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E32" s="2">
+        <v>7999000.0</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2">
+        <v>32.0</v>
+      </c>
+      <c r="B33" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="E33" s="2">
+        <v>8499000.0</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2">
+        <v>33.0</v>
+      </c>
+      <c r="B34" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E34" s="2">
+        <v>5499000.0</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2">
+        <v>34.0</v>
+      </c>
+      <c r="B35" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="E35" s="2">
+        <v>9999000.0</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2">
+        <v>35.0</v>
+      </c>
+      <c r="B36" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E36" s="2">
+        <v>1.0999E7</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2">
+        <v>36.0</v>
+      </c>
+      <c r="B37" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="E37" s="2">
+        <v>1.8999E7</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2">
+        <v>37.0</v>
+      </c>
+      <c r="B38" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E38" s="2">
+        <v>2.1999E7</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2">
+        <v>38.0</v>
+      </c>
+      <c r="B39" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E39" s="2">
+        <v>2.4999E7</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2">
+        <v>39.0</v>
+      </c>
+      <c r="B40" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E40" s="2">
+        <v>1.1999E7</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2">
+        <v>40.0</v>
+      </c>
+      <c r="B41" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E41" s="2">
+        <v>5999000.0</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2">
+        <v>41.0</v>
+      </c>
+      <c r="B42" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="E42" s="2">
+        <v>799000.0</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2">
+        <v>42.0</v>
+      </c>
+      <c r="B43" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="E43" s="2">
+        <v>1299000.0</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2">
+        <v>43.0</v>
+      </c>
+      <c r="B44" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="E44" s="2">
+        <v>699000.0</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2">
+        <v>44.0</v>
+      </c>
+      <c r="B45" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="E45" s="2">
+        <v>299000.0</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2">
+        <v>45.0</v>
+      </c>
+      <c r="B46" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E46" s="2">
+        <v>599000.0</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2">
+        <v>46.0</v>
+      </c>
+      <c r="B47" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E47" s="2">
+        <v>2499000.0</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2">
+        <v>47.0</v>
+      </c>
+      <c r="B48" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="E48" s="2">
+        <v>2699000.0</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2">
+        <v>48.0</v>
+      </c>
+      <c r="B49" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E49" s="2">
+        <v>2399000.0</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2">
+        <v>49.0</v>
+      </c>
+      <c r="B50" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="E50" s="2">
+        <v>3499000.0</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2">
+        <v>50.0</v>
+      </c>
+      <c r="B51" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E51" s="2">
+        <v>1799000.0</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4">
+        <v>51.0</v>
+      </c>
+      <c r="B52" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E52" s="4">
+        <v>3334.0</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4">
+        <v>52.0</v>
+      </c>
+      <c r="B53" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E53" s="4">
+        <v>31233.0</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink r:id="rId1" ref="F2"/>
+    <hyperlink r:id="rId2" ref="F3"/>
+    <hyperlink r:id="rId3" ref="F4"/>
+    <hyperlink r:id="rId4" ref="F5"/>
+    <hyperlink r:id="rId5" ref="F6"/>
+    <hyperlink r:id="rId6" ref="F7"/>
+    <hyperlink r:id="rId7" ref="F8"/>
+    <hyperlink r:id="rId8" ref="F9"/>
+    <hyperlink r:id="rId9" ref="F10"/>
+    <hyperlink r:id="rId10" ref="F11"/>
+    <hyperlink r:id="rId11" ref="F12"/>
+    <hyperlink r:id="rId12" ref="F13"/>
+    <hyperlink r:id="rId13" ref="F14"/>
+    <hyperlink r:id="rId14" ref="F15"/>
+    <hyperlink r:id="rId15" ref="F16"/>
+    <hyperlink r:id="rId16" ref="F17"/>
+    <hyperlink r:id="rId17" ref="F18"/>
+    <hyperlink r:id="rId18" ref="F19"/>
+    <hyperlink r:id="rId19" ref="F20"/>
+    <hyperlink r:id="rId20" ref="F21"/>
+    <hyperlink r:id="rId21" ref="F22"/>
+    <hyperlink r:id="rId22" ref="F23"/>
+    <hyperlink r:id="rId23" ref="F24"/>
+    <hyperlink r:id="rId24" ref="F25"/>
+    <hyperlink r:id="rId25" ref="F26"/>
+    <hyperlink r:id="rId26" ref="F27"/>
+    <hyperlink r:id="rId27" ref="F28"/>
+    <hyperlink r:id="rId28" ref="F29"/>
+    <hyperlink r:id="rId29" ref="F30"/>
+    <hyperlink r:id="rId30" ref="F31"/>
+    <hyperlink r:id="rId31" ref="F32"/>
+    <hyperlink r:id="rId32" ref="F33"/>
+    <hyperlink r:id="rId33" ref="F34"/>
+    <hyperlink r:id="rId34" ref="F35"/>
+    <hyperlink r:id="rId35" ref="F36"/>
+    <hyperlink r:id="rId36" ref="F37"/>
+    <hyperlink r:id="rId37" ref="F38"/>
+    <hyperlink r:id="rId38" ref="F39"/>
+    <hyperlink r:id="rId39" ref="F40"/>
+    <hyperlink r:id="rId40" ref="F41"/>
+    <hyperlink r:id="rId41" ref="F42"/>
+    <hyperlink r:id="rId42" ref="F43"/>
+    <hyperlink r:id="rId43" ref="F44"/>
+    <hyperlink r:id="rId44" ref="F45"/>
+    <hyperlink r:id="rId45" ref="F46"/>
+    <hyperlink r:id="rId46" ref="F47"/>
+    <hyperlink r:id="rId47" ref="F48"/>
+    <hyperlink r:id="rId48" ref="F49"/>
+    <hyperlink r:id="rId49" ref="F50"/>
+    <hyperlink r:id="rId50" ref="F51"/>
+    <hyperlink r:id="rId51" ref="F52"/>
+    <hyperlink r:id="rId52" ref="F53"/>
+  </hyperlinks>
+  <drawing r:id="rId53"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="B2" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="E2" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="H2" s="5">
+        <v>46179.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="B3" s="2">
+        <v>2.0</v>
+      </c>
       <c r="C3" s="2" t="s">
-        <v>25</v>
+        <v>246</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>26</v>
+        <v>247</v>
       </c>
       <c r="E3" s="2">
         <v>4.0</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>27</v>
+        <v>248</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H3" s="4">
+        <v>249</v>
+      </c>
+      <c r="H3" s="5">
         <v>46179.0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5">
+      <c r="A4" s="4">
         <v>3.0</v>
       </c>
       <c r="B4" s="2">
         <v>1.0</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>29</v>
+        <v>234</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>30</v>
+        <v>250</v>
       </c>
       <c r="E4" s="2">
         <v>5.0</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>31</v>
+        <v>251</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>32</v>
+        <v>252</v>
       </c>
       <c r="H4" s="6">
         <v>46179.832514837966</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5">
+      <c r="A5" s="4">
         <v>4.0</v>
       </c>
       <c r="B5" s="2">
         <v>2.0</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>21</v>
+        <v>242</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>30</v>
+        <v>250</v>
       </c>
       <c r="E5" s="2">
         <v>3.0</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>33</v>
+        <v>253</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>34</v>
+        <v>254</v>
       </c>
       <c r="H5" s="6">
         <v>46179.844965509255</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="B6" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="E6" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="H6" s="7">
+        <v>46180.01524305555</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="B7" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="E7" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="H7" s="7">
+        <v>46180.02484953704</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4">
+        <v>7.0</v>
+      </c>
+      <c r="B8" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="E8" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="H8" s="7">
+        <v>46180.025185185186</v>
       </c>
     </row>
   </sheetData>
